--- a/MaterialApi/Data/Consumption.xlsx
+++ b/MaterialApi/Data/Consumption.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\BDL\MaterialApi\MaterialApi\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D65698-D70D-4BB1-AEAA-D80AD03D3B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE3D1B9-3F87-450A-BA4C-E412F7698BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8AEDDDF1-D23C-4E65-972C-9FA5397ABD01}"/>
+    <workbookView xWindow="5580" yWindow="6840" windowWidth="21600" windowHeight="11385" xr2:uid="{8AEDDDF1-D23C-4E65-972C-9FA5397ABD01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>PO</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>SO202608210000000002</t>
-  </si>
-  <si>
-    <t>ID202608210002</t>
   </si>
   <si>
     <t>Copper</t>
@@ -123,8 +120,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -522,14 +520,14 @@
       <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1">
+        <v>20260821000123</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
       </c>
       <c r="F3" t="s">
         <v>15</v>

--- a/MaterialApi/Data/Consumption.xlsx
+++ b/MaterialApi/Data/Consumption.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\BDL\MaterialApi\MaterialApi\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\BDL\MaterialApi\MaterialApi\bin\Debug\net8.0\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE3D1B9-3F87-450A-BA4C-E412F7698BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166088D7-5504-4F5F-8547-4059FAAB585E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="6840" windowWidth="21600" windowHeight="11385" xr2:uid="{8AEDDDF1-D23C-4E65-972C-9FA5397ABD01}"/>
+    <workbookView xWindow="3615" yWindow="2430" windowWidth="21600" windowHeight="11385" xr2:uid="{8AEDDDF1-D23C-4E65-972C-9FA5397ABD01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
   <si>
     <t>PO</t>
   </si>
@@ -85,16 +85,76 @@
   </si>
   <si>
     <t>GRN-000002</t>
+  </si>
+  <si>
+    <t>PO202608210000000003</t>
+  </si>
+  <si>
+    <t>SO202608210000000003</t>
+  </si>
+  <si>
+    <t>GRN-000003</t>
+  </si>
+  <si>
+    <t>PO202608210000000004</t>
+  </si>
+  <si>
+    <t>SO202608210000000004</t>
+  </si>
+  <si>
+    <t>GRN-000005</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Anjana</t>
+  </si>
+  <si>
+    <t>Taurus</t>
+  </si>
+  <si>
+    <t>Arrow Engg</t>
+  </si>
+  <si>
+    <t>A.P.LMEC</t>
+  </si>
+  <si>
+    <t>PO202608210000000005</t>
+  </si>
+  <si>
+    <t>SO202608210000000006</t>
+  </si>
+  <si>
+    <t>GRN-000007</t>
+  </si>
+  <si>
+    <t>GRN-000008</t>
+  </si>
+  <si>
+    <t>PO202608210000000006</t>
+  </si>
+  <si>
+    <t>SO202608210000000007</t>
+  </si>
+  <si>
+    <t>Iron</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -437,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DC2F2C-54A8-4895-A8A2-16ABBF8E4EA0}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -449,7 +509,7 @@
     <col min="10" max="10" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,8 +540,11 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -512,8 +575,11 @@
       <c r="J2" t="s">
         <v>7</v>
       </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -544,8 +610,152 @@
       <c r="J3" t="s">
         <v>7</v>
       </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1">
+        <v>20260821000124</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>150</v>
+      </c>
+      <c r="H4">
+        <v>150</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1">
+        <v>20260821000125</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>150</v>
+      </c>
+      <c r="H5">
+        <v>150</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>20260821000127</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>150</v>
+      </c>
+      <c r="H6">
+        <v>150</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1">
+        <v>20260821000128</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>150</v>
+      </c>
+      <c r="H7">
+        <v>150</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>